--- a/artfynd/A 742-2026 artfynd.xlsx
+++ b/artfynd/A 742-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131389623</v>
       </c>
       <c r="B2" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131389591</v>
+        <v>131389576</v>
       </c>
       <c r="B3" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589298</v>
+        <v>589291</v>
       </c>
       <c r="R3" t="n">
-        <v>6402228</v>
+        <v>6402204</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131389576</v>
+        <v>131389591</v>
       </c>
       <c r="B4" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589291</v>
+        <v>589298</v>
       </c>
       <c r="R4" t="n">
-        <v>6402204</v>
+        <v>6402228</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
         <v>131389630</v>
       </c>
       <c r="B5" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>131389683</v>
       </c>
       <c r="B6" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>131389733</v>
       </c>
       <c r="B7" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1311,42 +1311,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131389855</v>
+        <v>131389654</v>
       </c>
       <c r="B8" t="n">
-        <v>57881</v>
+        <v>99021</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589291</v>
+        <v>589271</v>
       </c>
       <c r="R8" t="n">
-        <v>6402180</v>
+        <v>6402223</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,17 +1392,13 @@
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hästmyror i gran</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1424,7 +1420,7 @@
         <v>131389634</v>
       </c>
       <c r="B9" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1527,42 +1523,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131389654</v>
+        <v>131389855</v>
       </c>
       <c r="B10" t="n">
-        <v>99019</v>
+        <v>57883</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1570,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589271</v>
+        <v>589291</v>
       </c>
       <c r="R10" t="n">
-        <v>6402223</v>
+        <v>6402180</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,13 +1604,17 @@
           <t>2026-03-02</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hästmyror i gran</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1636,7 +1636,7 @@
         <v>131389690</v>
       </c>
       <c r="B11" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>131389756</v>
       </c>
       <c r="B12" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>131389785</v>
       </c>
       <c r="B13" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>131389548</v>
       </c>
       <c r="B14" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>131389669</v>
       </c>
       <c r="B15" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>131389611</v>
       </c>
       <c r="B16" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>131389535</v>
       </c>
       <c r="B17" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>131389662</v>
       </c>
       <c r="B18" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>131389563</v>
       </c>
       <c r="B19" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>131389913</v>
       </c>
       <c r="B20" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2693,10 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131389647</v>
+        <v>131389599</v>
       </c>
       <c r="B21" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2736,10 +2736,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589276</v>
+        <v>589292</v>
       </c>
       <c r="R21" t="n">
-        <v>6402220</v>
+        <v>6402232</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2799,10 +2799,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131389599</v>
+        <v>131389647</v>
       </c>
       <c r="B22" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2842,10 +2842,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589292</v>
+        <v>589276</v>
       </c>
       <c r="R22" t="n">
-        <v>6402232</v>
+        <v>6402220</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2908,7 +2908,7 @@
         <v>131389695</v>
       </c>
       <c r="B23" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 742-2026 artfynd.xlsx
+++ b/artfynd/A 742-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131389623</v>
       </c>
       <c r="B2" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>131389576</v>
       </c>
       <c r="B3" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>131389591</v>
       </c>
       <c r="B4" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>131389630</v>
       </c>
       <c r="B5" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>131389683</v>
       </c>
       <c r="B6" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>131389733</v>
       </c>
       <c r="B7" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>131389654</v>
       </c>
       <c r="B8" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>131389634</v>
       </c>
       <c r="B9" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>131389855</v>
       </c>
       <c r="B10" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>131389690</v>
       </c>
       <c r="B11" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>131389756</v>
       </c>
       <c r="B12" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>131389785</v>
       </c>
       <c r="B13" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>131389548</v>
       </c>
       <c r="B14" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>131389669</v>
       </c>
       <c r="B15" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>131389611</v>
       </c>
       <c r="B16" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>131389535</v>
       </c>
       <c r="B17" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>131389662</v>
       </c>
       <c r="B18" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>131389563</v>
       </c>
       <c r="B19" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>131389913</v>
       </c>
       <c r="B20" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>131389599</v>
       </c>
       <c r="B21" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>131389647</v>
       </c>
       <c r="B22" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>131389695</v>
       </c>
       <c r="B23" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 742-2026 artfynd.xlsx
+++ b/artfynd/A 742-2026 artfynd.xlsx
@@ -1311,42 +1311,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131389654</v>
+        <v>131389855</v>
       </c>
       <c r="B8" t="n">
-        <v>99022</v>
+        <v>57884</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589271</v>
+        <v>589291</v>
       </c>
       <c r="R8" t="n">
-        <v>6402223</v>
+        <v>6402180</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,13 +1392,17 @@
           <t>2026-03-02</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hästmyror i gran</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1417,7 +1421,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131389634</v>
+        <v>131389654</v>
       </c>
       <c r="B9" t="n">
         <v>99022</v>
@@ -1460,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589279</v>
+        <v>589271</v>
       </c>
       <c r="R9" t="n">
-        <v>6402230</v>
+        <v>6402223</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,42 +1527,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131389855</v>
+        <v>131389634</v>
       </c>
       <c r="B10" t="n">
-        <v>57884</v>
+        <v>99022</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1566,10 +1570,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589291</v>
+        <v>589279</v>
       </c>
       <c r="R10" t="n">
-        <v>6402180</v>
+        <v>6402230</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1604,17 +1608,13 @@
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Hästmyror i gran</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 742-2026 artfynd.xlsx
+++ b/artfynd/A 742-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131389623</v>
       </c>
       <c r="B2" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>131389576</v>
       </c>
       <c r="B3" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>131389591</v>
       </c>
       <c r="B4" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>131389630</v>
       </c>
       <c r="B5" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>131389683</v>
       </c>
       <c r="B6" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>131389733</v>
       </c>
       <c r="B7" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>131389855</v>
       </c>
       <c r="B8" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>131389654</v>
       </c>
       <c r="B9" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>131389634</v>
       </c>
       <c r="B10" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>131389690</v>
       </c>
       <c r="B11" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>131389756</v>
       </c>
       <c r="B12" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>131389785</v>
       </c>
       <c r="B13" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>131389548</v>
       </c>
       <c r="B14" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>131389669</v>
       </c>
       <c r="B15" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>131389611</v>
       </c>
       <c r="B16" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>131389535</v>
       </c>
       <c r="B17" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>131389662</v>
       </c>
       <c r="B18" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>131389563</v>
       </c>
       <c r="B19" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>131389913</v>
       </c>
       <c r="B20" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>131389599</v>
       </c>
       <c r="B21" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>131389647</v>
       </c>
       <c r="B22" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>131389695</v>
       </c>
       <c r="B23" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 742-2026 artfynd.xlsx
+++ b/artfynd/A 742-2026 artfynd.xlsx
@@ -1311,42 +1311,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131389855</v>
+        <v>131389634</v>
       </c>
       <c r="B8" t="n">
-        <v>57885</v>
+        <v>99023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589291</v>
+        <v>589279</v>
       </c>
       <c r="R8" t="n">
-        <v>6402180</v>
+        <v>6402230</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,17 +1392,13 @@
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hästmyror i gran</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1421,42 +1417,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131389654</v>
+        <v>131389855</v>
       </c>
       <c r="B9" t="n">
-        <v>99023</v>
+        <v>57885</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1464,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589271</v>
+        <v>589291</v>
       </c>
       <c r="R9" t="n">
-        <v>6402223</v>
+        <v>6402180</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1502,13 +1498,17 @@
           <t>2026-03-02</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hästmyror i gran</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1527,7 +1527,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131389634</v>
+        <v>131389654</v>
       </c>
       <c r="B10" t="n">
         <v>99023</v>
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589279</v>
+        <v>589271</v>
       </c>
       <c r="R10" t="n">
-        <v>6402230</v>
+        <v>6402223</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 742-2026 artfynd.xlsx
+++ b/artfynd/A 742-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131389623</v>
       </c>
       <c r="B2" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>131389576</v>
       </c>
       <c r="B3" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>131389591</v>
       </c>
       <c r="B4" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>131389630</v>
       </c>
       <c r="B5" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>131389683</v>
       </c>
       <c r="B6" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>131389733</v>
       </c>
       <c r="B7" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1311,42 +1311,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131389634</v>
+        <v>131389855</v>
       </c>
       <c r="B8" t="n">
-        <v>99023</v>
+        <v>57888</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589279</v>
+        <v>589291</v>
       </c>
       <c r="R8" t="n">
-        <v>6402230</v>
+        <v>6402180</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,13 +1392,17 @@
           <t>2026-03-02</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hästmyror i gran</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1417,42 +1421,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131389855</v>
+        <v>131389654</v>
       </c>
       <c r="B9" t="n">
-        <v>57885</v>
+        <v>99026</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1460,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589291</v>
+        <v>589271</v>
       </c>
       <c r="R9" t="n">
-        <v>6402180</v>
+        <v>6402223</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1498,17 +1502,13 @@
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Hästmyror i gran</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1527,10 +1527,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131389654</v>
+        <v>131389634</v>
       </c>
       <c r="B10" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589271</v>
+        <v>589279</v>
       </c>
       <c r="R10" t="n">
-        <v>6402223</v>
+        <v>6402230</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1636,7 +1636,7 @@
         <v>131389690</v>
       </c>
       <c r="B11" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>131389756</v>
       </c>
       <c r="B12" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>131389785</v>
       </c>
       <c r="B13" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>131389548</v>
       </c>
       <c r="B14" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>131389669</v>
       </c>
       <c r="B15" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>131389611</v>
       </c>
       <c r="B16" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>131389535</v>
       </c>
       <c r="B17" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>131389662</v>
       </c>
       <c r="B18" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>131389563</v>
       </c>
       <c r="B19" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>131389913</v>
       </c>
       <c r="B20" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>131389599</v>
       </c>
       <c r="B21" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>131389647</v>
       </c>
       <c r="B22" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>131389695</v>
       </c>
       <c r="B23" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 742-2026 artfynd.xlsx
+++ b/artfynd/A 742-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131389623</v>
       </c>
       <c r="B2" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>131389576</v>
       </c>
       <c r="B3" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>131389591</v>
       </c>
       <c r="B4" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>131389630</v>
       </c>
       <c r="B5" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>131389683</v>
       </c>
       <c r="B6" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>131389733</v>
       </c>
       <c r="B7" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>131389855</v>
       </c>
       <c r="B8" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>131389654</v>
       </c>
       <c r="B9" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>131389634</v>
       </c>
       <c r="B10" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>131389690</v>
       </c>
       <c r="B11" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>131389756</v>
       </c>
       <c r="B12" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>131389785</v>
       </c>
       <c r="B13" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>131389548</v>
       </c>
       <c r="B14" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>131389669</v>
       </c>
       <c r="B15" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>131389611</v>
       </c>
       <c r="B16" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>131389535</v>
       </c>
       <c r="B17" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>131389662</v>
       </c>
       <c r="B18" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>131389563</v>
       </c>
       <c r="B19" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>131389913</v>
       </c>
       <c r="B20" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>131389599</v>
       </c>
       <c r="B21" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>131389647</v>
       </c>
       <c r="B22" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>131389695</v>
       </c>
       <c r="B23" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 742-2026 artfynd.xlsx
+++ b/artfynd/A 742-2026 artfynd.xlsx
@@ -1311,42 +1311,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131389855</v>
+        <v>131389654</v>
       </c>
       <c r="B8" t="n">
-        <v>57889</v>
+        <v>99027</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589291</v>
+        <v>589271</v>
       </c>
       <c r="R8" t="n">
-        <v>6402180</v>
+        <v>6402223</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,17 +1392,13 @@
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hästmyror i gran</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1421,7 +1417,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131389654</v>
+        <v>131389634</v>
       </c>
       <c r="B9" t="n">
         <v>99027</v>
@@ -1464,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589271</v>
+        <v>589279</v>
       </c>
       <c r="R9" t="n">
-        <v>6402223</v>
+        <v>6402230</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1527,42 +1523,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131389634</v>
+        <v>131389855</v>
       </c>
       <c r="B10" t="n">
-        <v>99027</v>
+        <v>57889</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1570,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589279</v>
+        <v>589291</v>
       </c>
       <c r="R10" t="n">
-        <v>6402230</v>
+        <v>6402180</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,13 +1604,17 @@
           <t>2026-03-02</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hästmyror i gran</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 742-2026 artfynd.xlsx
+++ b/artfynd/A 742-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131389623</v>
       </c>
       <c r="B2" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>131389576</v>
       </c>
       <c r="B3" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>131389591</v>
       </c>
       <c r="B4" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>131389630</v>
       </c>
       <c r="B5" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>131389683</v>
       </c>
       <c r="B6" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>131389733</v>
       </c>
       <c r="B7" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1311,42 +1311,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131389654</v>
+        <v>131389855</v>
       </c>
       <c r="B8" t="n">
-        <v>99027</v>
+        <v>57895</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589271</v>
+        <v>589291</v>
       </c>
       <c r="R8" t="n">
-        <v>6402223</v>
+        <v>6402180</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,13 +1392,17 @@
           <t>2026-03-02</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hästmyror i gran</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1417,10 +1421,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131389634</v>
+        <v>131389654</v>
       </c>
       <c r="B9" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1460,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589279</v>
+        <v>589271</v>
       </c>
       <c r="R9" t="n">
-        <v>6402230</v>
+        <v>6402223</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,42 +1527,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131389855</v>
+        <v>131389634</v>
       </c>
       <c r="B10" t="n">
-        <v>57889</v>
+        <v>99033</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1566,10 +1570,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589291</v>
+        <v>589279</v>
       </c>
       <c r="R10" t="n">
-        <v>6402180</v>
+        <v>6402230</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1604,17 +1608,13 @@
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Hästmyror i gran</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1636,7 +1636,7 @@
         <v>131389690</v>
       </c>
       <c r="B11" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>131389756</v>
       </c>
       <c r="B12" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>131389785</v>
       </c>
       <c r="B13" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>131389548</v>
       </c>
       <c r="B14" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>131389669</v>
       </c>
       <c r="B15" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>131389611</v>
       </c>
       <c r="B16" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>131389535</v>
       </c>
       <c r="B17" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>131389662</v>
       </c>
       <c r="B18" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>131389563</v>
       </c>
       <c r="B19" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>131389913</v>
       </c>
       <c r="B20" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>131389599</v>
       </c>
       <c r="B21" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>131389647</v>
       </c>
       <c r="B22" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>131389695</v>
       </c>
       <c r="B23" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 742-2026 artfynd.xlsx
+++ b/artfynd/A 742-2026 artfynd.xlsx
@@ -1311,42 +1311,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131389855</v>
+        <v>131389654</v>
       </c>
       <c r="B8" t="n">
-        <v>57895</v>
+        <v>99033</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589291</v>
+        <v>589271</v>
       </c>
       <c r="R8" t="n">
-        <v>6402180</v>
+        <v>6402223</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,17 +1392,13 @@
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hästmyror i gran</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1421,7 +1417,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131389654</v>
+        <v>131389634</v>
       </c>
       <c r="B9" t="n">
         <v>99033</v>
@@ -1464,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589271</v>
+        <v>589279</v>
       </c>
       <c r="R9" t="n">
-        <v>6402223</v>
+        <v>6402230</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1527,42 +1523,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131389634</v>
+        <v>131389855</v>
       </c>
       <c r="B10" t="n">
-        <v>99033</v>
+        <v>57895</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1570,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589279</v>
+        <v>589291</v>
       </c>
       <c r="R10" t="n">
-        <v>6402230</v>
+        <v>6402180</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,13 +1604,17 @@
           <t>2026-03-02</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hästmyror i gran</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 742-2026 artfynd.xlsx
+++ b/artfynd/A 742-2026 artfynd.xlsx
@@ -2693,7 +2693,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131389599</v>
+        <v>131389647</v>
       </c>
       <c r="B21" t="n">
         <v>99033</v>
@@ -2736,10 +2736,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589292</v>
+        <v>589276</v>
       </c>
       <c r="R21" t="n">
-        <v>6402232</v>
+        <v>6402220</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2799,7 +2799,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131389647</v>
+        <v>131389599</v>
       </c>
       <c r="B22" t="n">
         <v>99033</v>
@@ -2842,10 +2842,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589276</v>
+        <v>589292</v>
       </c>
       <c r="R22" t="n">
-        <v>6402220</v>
+        <v>6402232</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 742-2026 artfynd.xlsx
+++ b/artfynd/A 742-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131389623</v>
       </c>
       <c r="B2" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>131389576</v>
       </c>
       <c r="B3" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>131389591</v>
       </c>
       <c r="B4" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>131389630</v>
       </c>
       <c r="B5" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>131389683</v>
       </c>
       <c r="B6" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>131389733</v>
       </c>
       <c r="B7" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1311,42 +1311,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131389654</v>
+        <v>131389855</v>
       </c>
       <c r="B8" t="n">
-        <v>99033</v>
+        <v>57895</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589271</v>
+        <v>589291</v>
       </c>
       <c r="R8" t="n">
-        <v>6402223</v>
+        <v>6402180</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,13 +1392,17 @@
           <t>2026-03-02</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hästmyror i gran</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1417,10 +1421,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131389634</v>
+        <v>131389654</v>
       </c>
       <c r="B9" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1460,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589279</v>
+        <v>589271</v>
       </c>
       <c r="R9" t="n">
-        <v>6402230</v>
+        <v>6402223</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,42 +1527,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131389855</v>
+        <v>131389634</v>
       </c>
       <c r="B10" t="n">
-        <v>57895</v>
+        <v>99034</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1566,10 +1570,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589291</v>
+        <v>589279</v>
       </c>
       <c r="R10" t="n">
-        <v>6402180</v>
+        <v>6402230</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1604,17 +1608,13 @@
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Hästmyror i gran</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1636,7 +1636,7 @@
         <v>131389690</v>
       </c>
       <c r="B11" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>131389756</v>
       </c>
       <c r="B12" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>131389785</v>
       </c>
       <c r="B13" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>131389548</v>
       </c>
       <c r="B14" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>131389669</v>
       </c>
       <c r="B15" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>131389611</v>
       </c>
       <c r="B16" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>131389535</v>
       </c>
       <c r="B17" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>131389662</v>
       </c>
       <c r="B18" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>131389563</v>
       </c>
       <c r="B19" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>131389913</v>
       </c>
       <c r="B20" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2693,10 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131389647</v>
+        <v>131389599</v>
       </c>
       <c r="B21" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2736,10 +2736,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589276</v>
+        <v>589292</v>
       </c>
       <c r="R21" t="n">
-        <v>6402220</v>
+        <v>6402232</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2799,10 +2799,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131389599</v>
+        <v>131389647</v>
       </c>
       <c r="B22" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2842,10 +2842,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589292</v>
+        <v>589276</v>
       </c>
       <c r="R22" t="n">
-        <v>6402232</v>
+        <v>6402220</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2908,7 +2908,7 @@
         <v>131389695</v>
       </c>
       <c r="B23" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 742-2026 artfynd.xlsx
+++ b/artfynd/A 742-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131389623</v>
       </c>
       <c r="B2" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>131389576</v>
       </c>
       <c r="B3" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>131389591</v>
       </c>
       <c r="B4" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>131389630</v>
       </c>
       <c r="B5" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>131389683</v>
       </c>
       <c r="B6" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>131389733</v>
       </c>
       <c r="B7" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>131389855</v>
       </c>
       <c r="B8" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>131389654</v>
       </c>
       <c r="B9" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>131389634</v>
       </c>
       <c r="B10" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>131389690</v>
       </c>
       <c r="B11" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>131389756</v>
       </c>
       <c r="B12" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>131389785</v>
       </c>
       <c r="B13" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>131389548</v>
       </c>
       <c r="B14" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>131389669</v>
       </c>
       <c r="B15" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>131389611</v>
       </c>
       <c r="B16" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>131389535</v>
       </c>
       <c r="B17" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>131389662</v>
       </c>
       <c r="B18" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>131389563</v>
       </c>
       <c r="B19" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>131389913</v>
       </c>
       <c r="B20" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>131389599</v>
       </c>
       <c r="B21" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>131389647</v>
       </c>
       <c r="B22" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>131389695</v>
       </c>
       <c r="B23" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 742-2026 artfynd.xlsx
+++ b/artfynd/A 742-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131389623</v>
       </c>
       <c r="B2" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>131389576</v>
       </c>
       <c r="B3" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>131389591</v>
       </c>
       <c r="B4" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>131389630</v>
       </c>
       <c r="B5" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>131389683</v>
       </c>
       <c r="B6" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>131389733</v>
       </c>
       <c r="B7" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1311,42 +1311,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131389855</v>
+        <v>131389654</v>
       </c>
       <c r="B8" t="n">
-        <v>57896</v>
+        <v>99038</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589291</v>
+        <v>589271</v>
       </c>
       <c r="R8" t="n">
-        <v>6402180</v>
+        <v>6402223</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,17 +1392,13 @@
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hästmyror i gran</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1421,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131389654</v>
+        <v>131389634</v>
       </c>
       <c r="B9" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589271</v>
+        <v>589279</v>
       </c>
       <c r="R9" t="n">
-        <v>6402223</v>
+        <v>6402230</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1527,42 +1523,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131389634</v>
+        <v>131389855</v>
       </c>
       <c r="B10" t="n">
-        <v>99035</v>
+        <v>57899</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1570,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589279</v>
+        <v>589291</v>
       </c>
       <c r="R10" t="n">
-        <v>6402230</v>
+        <v>6402180</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,13 +1604,17 @@
           <t>2026-03-02</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hästmyror i gran</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1636,7 +1636,7 @@
         <v>131389690</v>
       </c>
       <c r="B11" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>131389756</v>
       </c>
       <c r="B12" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>131389785</v>
       </c>
       <c r="B13" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>131389548</v>
       </c>
       <c r="B14" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>131389669</v>
       </c>
       <c r="B15" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>131389611</v>
       </c>
       <c r="B16" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>131389535</v>
       </c>
       <c r="B17" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>131389662</v>
       </c>
       <c r="B18" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>131389563</v>
       </c>
       <c r="B19" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>131389913</v>
       </c>
       <c r="B20" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>131389599</v>
       </c>
       <c r="B21" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>131389647</v>
       </c>
       <c r="B22" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>131389695</v>
       </c>
       <c r="B23" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 742-2026 artfynd.xlsx
+++ b/artfynd/A 742-2026 artfynd.xlsx
@@ -1311,42 +1311,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131389654</v>
+        <v>131389855</v>
       </c>
       <c r="B8" t="n">
-        <v>99038</v>
+        <v>57899</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589271</v>
+        <v>589291</v>
       </c>
       <c r="R8" t="n">
-        <v>6402223</v>
+        <v>6402180</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,13 +1392,17 @@
           <t>2026-03-02</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hästmyror i gran</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1417,7 +1421,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131389634</v>
+        <v>131389654</v>
       </c>
       <c r="B9" t="n">
         <v>99038</v>
@@ -1460,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589279</v>
+        <v>589271</v>
       </c>
       <c r="R9" t="n">
-        <v>6402230</v>
+        <v>6402223</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,42 +1527,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131389855</v>
+        <v>131389634</v>
       </c>
       <c r="B10" t="n">
-        <v>57899</v>
+        <v>99038</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1566,10 +1570,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589291</v>
+        <v>589279</v>
       </c>
       <c r="R10" t="n">
-        <v>6402180</v>
+        <v>6402230</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1604,17 +1608,13 @@
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Hästmyror i gran</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 742-2026 artfynd.xlsx
+++ b/artfynd/A 742-2026 artfynd.xlsx
@@ -1311,42 +1311,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131389855</v>
+        <v>131389654</v>
       </c>
       <c r="B8" t="n">
-        <v>57899</v>
+        <v>99038</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589291</v>
+        <v>589271</v>
       </c>
       <c r="R8" t="n">
-        <v>6402180</v>
+        <v>6402223</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,17 +1392,13 @@
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hästmyror i gran</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1421,7 +1417,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131389654</v>
+        <v>131389634</v>
       </c>
       <c r="B9" t="n">
         <v>99038</v>
@@ -1464,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589271</v>
+        <v>589279</v>
       </c>
       <c r="R9" t="n">
-        <v>6402223</v>
+        <v>6402230</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1527,42 +1523,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131389634</v>
+        <v>131389855</v>
       </c>
       <c r="B10" t="n">
-        <v>99038</v>
+        <v>57899</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1570,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589279</v>
+        <v>589291</v>
       </c>
       <c r="R10" t="n">
-        <v>6402230</v>
+        <v>6402180</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,13 +1604,17 @@
           <t>2026-03-02</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hästmyror i gran</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 742-2026 artfynd.xlsx
+++ b/artfynd/A 742-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131389623</v>
       </c>
       <c r="B2" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>131389576</v>
       </c>
       <c r="B3" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>131389591</v>
       </c>
       <c r="B4" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>131389630</v>
       </c>
       <c r="B5" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>131389683</v>
       </c>
       <c r="B6" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>131389733</v>
       </c>
       <c r="B7" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>131389654</v>
       </c>
       <c r="B8" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>131389634</v>
       </c>
       <c r="B9" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>131389855</v>
       </c>
       <c r="B10" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>131389690</v>
       </c>
       <c r="B11" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>131389756</v>
       </c>
       <c r="B12" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>131389785</v>
       </c>
       <c r="B13" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>131389548</v>
       </c>
       <c r="B14" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>131389669</v>
       </c>
       <c r="B15" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>131389611</v>
       </c>
       <c r="B16" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>131389535</v>
       </c>
       <c r="B17" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>131389662</v>
       </c>
       <c r="B18" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>131389563</v>
       </c>
       <c r="B19" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>131389913</v>
       </c>
       <c r="B20" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2693,10 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131389599</v>
+        <v>131389647</v>
       </c>
       <c r="B21" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2736,10 +2736,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589292</v>
+        <v>589276</v>
       </c>
       <c r="R21" t="n">
-        <v>6402232</v>
+        <v>6402220</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2799,10 +2799,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131389647</v>
+        <v>131389599</v>
       </c>
       <c r="B22" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2842,10 +2842,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589276</v>
+        <v>589292</v>
       </c>
       <c r="R22" t="n">
-        <v>6402220</v>
+        <v>6402232</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2908,7 +2908,7 @@
         <v>131389695</v>
       </c>
       <c r="B23" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 742-2026 artfynd.xlsx
+++ b/artfynd/A 742-2026 artfynd.xlsx
@@ -1311,42 +1311,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131389654</v>
+        <v>131389855</v>
       </c>
       <c r="B8" t="n">
-        <v>99044</v>
+        <v>57901</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589271</v>
+        <v>589291</v>
       </c>
       <c r="R8" t="n">
-        <v>6402223</v>
+        <v>6402180</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,13 +1392,17 @@
           <t>2026-03-02</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hästmyror i gran</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1417,7 +1421,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131389634</v>
+        <v>131389654</v>
       </c>
       <c r="B9" t="n">
         <v>99044</v>
@@ -1460,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589279</v>
+        <v>589271</v>
       </c>
       <c r="R9" t="n">
-        <v>6402230</v>
+        <v>6402223</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,42 +1527,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131389855</v>
+        <v>131389634</v>
       </c>
       <c r="B10" t="n">
-        <v>57901</v>
+        <v>99044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1566,10 +1570,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589291</v>
+        <v>589279</v>
       </c>
       <c r="R10" t="n">
-        <v>6402180</v>
+        <v>6402230</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1604,17 +1608,13 @@
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Hästmyror i gran</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 742-2026 artfynd.xlsx
+++ b/artfynd/A 742-2026 artfynd.xlsx
@@ -1311,42 +1311,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131389855</v>
+        <v>131389654</v>
       </c>
       <c r="B8" t="n">
-        <v>57901</v>
+        <v>99044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589291</v>
+        <v>589271</v>
       </c>
       <c r="R8" t="n">
-        <v>6402180</v>
+        <v>6402223</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,17 +1392,13 @@
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hästmyror i gran</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1421,7 +1417,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131389654</v>
+        <v>131389634</v>
       </c>
       <c r="B9" t="n">
         <v>99044</v>
@@ -1464,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589271</v>
+        <v>589279</v>
       </c>
       <c r="R9" t="n">
-        <v>6402223</v>
+        <v>6402230</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1527,42 +1523,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131389634</v>
+        <v>131389855</v>
       </c>
       <c r="B10" t="n">
-        <v>99044</v>
+        <v>57901</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1570,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589279</v>
+        <v>589291</v>
       </c>
       <c r="R10" t="n">
-        <v>6402230</v>
+        <v>6402180</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,13 +1604,17 @@
           <t>2026-03-02</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hästmyror i gran</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
